--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/66.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/66.xlsx
@@ -426,13 +426,13 @@
         <v>-15.05178696259867</v>
       </c>
       <c r="E2">
-        <v>-6.544403272950549</v>
+        <v>-10.18148340000306</v>
       </c>
       <c r="F2">
-        <v>-1.097892623528486</v>
+        <v>-2.304746891238905</v>
       </c>
       <c r="G2">
-        <v>-14.29484740451176</v>
+        <v>-17.15239113437124</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.49183849222738</v>
       </c>
       <c r="E3">
-        <v>-6.416904087264591</v>
+        <v>-9.929559862482348</v>
       </c>
       <c r="F3">
-        <v>-0.6750988713440348</v>
+        <v>-2.196205082082683</v>
       </c>
       <c r="G3">
-        <v>-13.08196945638005</v>
+        <v>-16.95826074394837</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-13.81954152345945</v>
       </c>
       <c r="E4">
-        <v>-7.154560803796038</v>
+        <v>-9.851049708611368</v>
       </c>
       <c r="F4">
-        <v>-0.963105649949367</v>
+        <v>-2.196646601908375</v>
       </c>
       <c r="G4">
-        <v>-13.21155414042375</v>
+        <v>-17.14381351087898</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-13.11789642157001</v>
       </c>
       <c r="E5">
-        <v>-7.635068123801925</v>
+        <v>-11.49292947262439</v>
       </c>
       <c r="F5">
-        <v>-0.8122798267172442</v>
+        <v>-1.979617655844516</v>
       </c>
       <c r="G5">
-        <v>-13.11848477367821</v>
+        <v>-16.06305446940128</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.39259864526034</v>
       </c>
       <c r="E6">
-        <v>-8.807770809776255</v>
+        <v>-11.60181663013883</v>
       </c>
       <c r="F6">
-        <v>-0.6984406080201193</v>
+        <v>-1.790654625754907</v>
       </c>
       <c r="G6">
-        <v>-12.38790696298077</v>
+        <v>-16.01919139627871</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-11.68079803581366</v>
       </c>
       <c r="E7">
-        <v>-10.2032336606619</v>
+        <v>-11.98588103920336</v>
       </c>
       <c r="F7">
-        <v>-0.2064317891273529</v>
+        <v>-1.791446544991983</v>
       </c>
       <c r="G7">
-        <v>-12.32908187929346</v>
+        <v>-14.74837890120975</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-10.9998791345211</v>
       </c>
       <c r="E8">
-        <v>-11.32677523280896</v>
+        <v>-13.40828378196063</v>
       </c>
       <c r="F8">
-        <v>-0.1381610612582289</v>
+        <v>-2.109652285633774</v>
       </c>
       <c r="G8">
-        <v>-11.11125135503501</v>
+        <v>-15.41741035978661</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-10.37602886762702</v>
       </c>
       <c r="E9">
-        <v>-11.43166827624863</v>
+        <v>-13.94397055774998</v>
       </c>
       <c r="F9">
-        <v>-0.05297424265653614</v>
+        <v>-1.576640108669835</v>
       </c>
       <c r="G9">
-        <v>-10.60059970560242</v>
+        <v>-14.2766923727744</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.826608930209423</v>
       </c>
       <c r="E10">
-        <v>-13.48208432286364</v>
+        <v>-14.03488420192797</v>
       </c>
       <c r="F10">
-        <v>-0.4298582166430328</v>
+        <v>-1.64138116303563</v>
       </c>
       <c r="G10">
-        <v>-10.34172497606803</v>
+        <v>-13.92526803214414</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.367879536370117</v>
       </c>
       <c r="E11">
-        <v>-13.01975882599855</v>
+        <v>-13.92495096691777</v>
       </c>
       <c r="F11">
-        <v>-0.2690199166132724</v>
+        <v>-1.594288476186478</v>
       </c>
       <c r="G11">
-        <v>-10.2292491913713</v>
+        <v>-13.51697514024029</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.014951298481684</v>
       </c>
       <c r="E12">
-        <v>-13.97745862303671</v>
+        <v>-15.25810654393187</v>
       </c>
       <c r="F12">
-        <v>-0.03747134671314339</v>
+        <v>-1.569434969000285</v>
       </c>
       <c r="G12">
-        <v>-9.241498271546648</v>
+        <v>-13.06614835924788</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.773130941659883</v>
       </c>
       <c r="E13">
-        <v>-14.93466934488203</v>
+        <v>-16.70737672297666</v>
       </c>
       <c r="F13">
-        <v>-0.6644170736849352</v>
+        <v>-1.318013036739593</v>
       </c>
       <c r="G13">
-        <v>-9.905775786729109</v>
+        <v>-12.28103262133648</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.649990509423967</v>
       </c>
       <c r="E14">
-        <v>-13.68844235491917</v>
+        <v>-16.65749105330816</v>
       </c>
       <c r="F14">
-        <v>0.009685952793426867</v>
+        <v>-1.156460684008619</v>
       </c>
       <c r="G14">
-        <v>-7.629941255757131</v>
+        <v>-11.88817018219117</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.634854511388923</v>
       </c>
       <c r="E15">
-        <v>-17.32562210839984</v>
+        <v>-17.38405753699482</v>
       </c>
       <c r="F15">
-        <v>-0.2723714911249992</v>
+        <v>-0.4926526076122493</v>
       </c>
       <c r="G15">
-        <v>-7.396153840319339</v>
+        <v>-11.81902281751241</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-8.717311618686381</v>
       </c>
       <c r="E16">
-        <v>-16.97628656650014</v>
+        <v>-18.57560773178908</v>
       </c>
       <c r="F16">
-        <v>0.608399261943006</v>
+        <v>-0.7586057608528503</v>
       </c>
       <c r="G16">
-        <v>-7.163376141271025</v>
+        <v>-11.64569920580387</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-8.869542393568882</v>
       </c>
       <c r="E17">
-        <v>-17.78749475786417</v>
+        <v>-19.31259423416739</v>
       </c>
       <c r="F17">
-        <v>0.4422726644137735</v>
+        <v>-0.5247004856917566</v>
       </c>
       <c r="G17">
-        <v>-7.142923590929407</v>
+        <v>-11.6754510785653</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.067811521085059</v>
       </c>
       <c r="E18">
-        <v>-19.3116568400478</v>
+        <v>-19.95054300999795</v>
       </c>
       <c r="F18">
-        <v>1.300144857366192</v>
+        <v>-0.3222392087735294</v>
       </c>
       <c r="G18">
-        <v>-6.246010730156822</v>
+        <v>-11.18866184137978</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.277327023282675</v>
       </c>
       <c r="E19">
-        <v>-19.45223878714192</v>
+        <v>-20.07795615467776</v>
       </c>
       <c r="F19">
-        <v>0.9259083455990424</v>
+        <v>0.2056495158040947</v>
       </c>
       <c r="G19">
-        <v>-7.100644613847375</v>
+        <v>-10.86462564399592</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.473981438073528</v>
       </c>
       <c r="E20">
-        <v>-20.51307457970477</v>
+        <v>-21.06116484580113</v>
       </c>
       <c r="F20">
-        <v>1.520913053886288</v>
+        <v>0.4555066620408984</v>
       </c>
       <c r="G20">
-        <v>-6.670217414467953</v>
+        <v>-11.51998123895004</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.628920664319899</v>
       </c>
       <c r="E21">
-        <v>-21.35220987027411</v>
+        <v>-22.24258484424023</v>
       </c>
       <c r="F21">
-        <v>1.411742513871341</v>
+        <v>0.6131383518544219</v>
       </c>
       <c r="G21">
-        <v>-6.455260382057536</v>
+        <v>-10.4000236830146</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.728813472725713</v>
       </c>
       <c r="E22">
-        <v>-20.89694879286098</v>
+        <v>-22.36186032112826</v>
       </c>
       <c r="F22">
-        <v>1.679167675986717</v>
+        <v>0.9325071203297433</v>
       </c>
       <c r="G22">
-        <v>-6.96984827013631</v>
+        <v>-10.65659427285366</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.760185131895803</v>
       </c>
       <c r="E23">
-        <v>-21.80829060148262</v>
+        <v>-23.20199187597928</v>
       </c>
       <c r="F23">
-        <v>1.722633770346413</v>
+        <v>1.066235440368084</v>
       </c>
       <c r="G23">
-        <v>-6.465695221597318</v>
+        <v>-10.94275782926826</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.726878568291736</v>
       </c>
       <c r="E24">
-        <v>-21.81910912588694</v>
+        <v>-22.98579799837909</v>
       </c>
       <c r="F24">
-        <v>1.78446974023059</v>
+        <v>1.079893562105443</v>
       </c>
       <c r="G24">
-        <v>-5.63348035229871</v>
+        <v>-10.89794297430314</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-9.633813872384932</v>
       </c>
       <c r="E25">
-        <v>-22.19632195377787</v>
+        <v>-23.03300733990905</v>
       </c>
       <c r="F25">
-        <v>1.875336674113279</v>
+        <v>1.051401036918751</v>
       </c>
       <c r="G25">
-        <v>-6.345413170518978</v>
+        <v>-11.02070793453594</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.501818630759246</v>
       </c>
       <c r="E26">
-        <v>-22.39080632698528</v>
+        <v>-23.02952494339715</v>
       </c>
       <c r="F26">
-        <v>1.972921667632672</v>
+        <v>0.5171960108947804</v>
       </c>
       <c r="G26">
-        <v>-6.944509354578728</v>
+        <v>-11.11937874433391</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.348070884242675</v>
       </c>
       <c r="E27">
-        <v>-22.67949654497427</v>
+        <v>-23.18316248105538</v>
       </c>
       <c r="F27">
-        <v>1.638239699349199</v>
+        <v>0.979621344731368</v>
       </c>
       <c r="G27">
-        <v>-7.247603040881162</v>
+        <v>-10.69397695308311</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.198615055707066</v>
       </c>
       <c r="E28">
-        <v>-22.83888977309625</v>
+        <v>-22.48367174346058</v>
       </c>
       <c r="F28">
-        <v>1.193485927316533</v>
+        <v>1.161212733303464</v>
       </c>
       <c r="G28">
-        <v>-6.664152495040009</v>
+        <v>-10.91421099508312</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.07138248894951</v>
       </c>
       <c r="E29">
-        <v>-22.47239131470748</v>
+        <v>-22.53765115363201</v>
       </c>
       <c r="F29">
-        <v>1.33969111717584</v>
+        <v>0.8166649092526492</v>
       </c>
       <c r="G29">
-        <v>-6.379915676129262</v>
+        <v>-10.66690331166295</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.98458989108407</v>
       </c>
       <c r="E30">
-        <v>-22.4005561315238</v>
+        <v>-22.01148775868079</v>
       </c>
       <c r="F30">
-        <v>1.285635173938756</v>
+        <v>0.5401061681540062</v>
       </c>
       <c r="G30">
-        <v>-6.662762065913514</v>
+        <v>-10.31085744945987</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.944656101517802</v>
       </c>
       <c r="E31">
-        <v>-21.56827242212807</v>
+        <v>-21.70883625532616</v>
       </c>
       <c r="F31">
-        <v>1.541671941000444</v>
+        <v>0.5262318425245174</v>
       </c>
       <c r="G31">
-        <v>-5.917972083215979</v>
+        <v>-10.04836098310552</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.951052815079471</v>
       </c>
       <c r="E32">
-        <v>-21.04775603426442</v>
+        <v>-21.88878875544297</v>
       </c>
       <c r="F32">
-        <v>1.119050489235775</v>
+        <v>0.299390884574498</v>
       </c>
       <c r="G32">
-        <v>-5.864126060019733</v>
+        <v>-10.54241024665865</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.993962239326942</v>
       </c>
       <c r="E33">
-        <v>-20.20534665698754</v>
+        <v>-21.17931273266125</v>
       </c>
       <c r="F33">
-        <v>1.768631355489064</v>
+        <v>0.6054751250111237</v>
       </c>
       <c r="G33">
-        <v>-5.904719969422277</v>
+        <v>-9.865406994423235</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.05543931308924</v>
       </c>
       <c r="E34">
-        <v>-21.25154189308359</v>
+        <v>-20.36853474632795</v>
       </c>
       <c r="F34">
-        <v>1.55513125456113</v>
+        <v>0.7430512116354684</v>
       </c>
       <c r="G34">
-        <v>-5.156741931370423</v>
+        <v>-9.93729218026297</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.11693690077276</v>
       </c>
       <c r="E35">
-        <v>-18.72070909594285</v>
+        <v>-21.0606757706083</v>
       </c>
       <c r="F35">
-        <v>1.961568064009902</v>
+        <v>0.5488835491540699</v>
       </c>
       <c r="G35">
-        <v>-7.187086268423285</v>
+        <v>-9.74147010106954</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.154902048250495</v>
       </c>
       <c r="E36">
-        <v>-18.8131307219654</v>
+        <v>-20.26974608585062</v>
       </c>
       <c r="F36">
-        <v>1.575247328570713</v>
+        <v>0.8188899040965687</v>
       </c>
       <c r="G36">
-        <v>-5.808343367683014</v>
+        <v>-10.17498934998264</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.155579909497932</v>
       </c>
       <c r="E37">
-        <v>-19.87270759875411</v>
+        <v>-20.11039814246872</v>
       </c>
       <c r="F37">
-        <v>2.178472754963341</v>
+        <v>0.8366948330523413</v>
       </c>
       <c r="G37">
-        <v>-5.602798216240744</v>
+        <v>-9.112949788256749</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.105023609299177</v>
       </c>
       <c r="E38">
-        <v>-17.76888725816665</v>
+        <v>-20.23859018467785</v>
       </c>
       <c r="F38">
-        <v>1.941147150796088</v>
+        <v>0.7144319462361483</v>
       </c>
       <c r="G38">
-        <v>-7.580455221036106</v>
+        <v>-9.048847694979841</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.004217648403975</v>
       </c>
       <c r="E39">
-        <v>-17.86172097532389</v>
+        <v>-19.6033041515638</v>
       </c>
       <c r="F39">
-        <v>1.658077441911441</v>
+        <v>0.7891216931095657</v>
       </c>
       <c r="G39">
-        <v>-6.447358109855295</v>
+        <v>-9.468227603894714</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.853265992743145</v>
       </c>
       <c r="E40">
-        <v>-18.91200542344887</v>
+        <v>-18.43906971198381</v>
       </c>
       <c r="F40">
-        <v>1.508515707335991</v>
+        <v>0.5652040437240258</v>
       </c>
       <c r="G40">
-        <v>-5.438144923299553</v>
+        <v>-9.425978421722535</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.66565720867459</v>
       </c>
       <c r="E41">
-        <v>-17.75560977237616</v>
+        <v>-17.68736114060656</v>
       </c>
       <c r="F41">
-        <v>1.701308279928742</v>
+        <v>0.5841222984691609</v>
       </c>
       <c r="G41">
-        <v>-5.764736861839734</v>
+        <v>-9.684707487253197</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.450784732864435</v>
       </c>
       <c r="E42">
-        <v>-17.5100894971023</v>
+        <v>-16.89476497741406</v>
       </c>
       <c r="F42">
-        <v>1.93015802883055</v>
+        <v>0.7604270462765909</v>
       </c>
       <c r="G42">
-        <v>-5.675938098839863</v>
+        <v>-8.888875513431177</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.227834721545316</v>
       </c>
       <c r="E43">
-        <v>-16.84837528967948</v>
+        <v>-17.8352792155931</v>
       </c>
       <c r="F43">
-        <v>1.645989904769791</v>
+        <v>0.6453369928012387</v>
       </c>
       <c r="G43">
-        <v>-5.956390964199222</v>
+        <v>-8.911029684179981</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.008076158300009</v>
       </c>
       <c r="E44">
-        <v>-14.7838077617905</v>
+        <v>-16.06194690808542</v>
       </c>
       <c r="F44">
-        <v>1.596602640214885</v>
+        <v>0.5563769606797941</v>
       </c>
       <c r="G44">
-        <v>-6.761369975346246</v>
+        <v>-8.714856687159388</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.808234096456697</v>
       </c>
       <c r="E45">
-        <v>-13.64935256728496</v>
+        <v>-16.06006306289823</v>
       </c>
       <c r="F45">
-        <v>1.984997607630683</v>
+        <v>0.464523441220371</v>
       </c>
       <c r="G45">
-        <v>-7.119716666699117</v>
+        <v>-8.798421477661671</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.634764927122834</v>
       </c>
       <c r="E46">
-        <v>-14.6468350084805</v>
+        <v>-15.20241084211154</v>
       </c>
       <c r="F46">
-        <v>1.582490573140792</v>
+        <v>0.1847845976623808</v>
       </c>
       <c r="G46">
-        <v>-6.754417829713777</v>
+        <v>-8.726423733273602</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-7.496573183907147</v>
       </c>
       <c r="E47">
-        <v>-12.84660809384126</v>
+        <v>-15.45066631568603</v>
       </c>
       <c r="F47">
-        <v>1.269175513645129</v>
+        <v>0.1471270155311152</v>
       </c>
       <c r="G47">
-        <v>-4.599805544753292</v>
+        <v>-9.286273399965291</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-7.393571338443589</v>
       </c>
       <c r="E48">
-        <v>-14.43834406516735</v>
+        <v>-14.90158431378199</v>
       </c>
       <c r="F48">
-        <v>1.459570790974179</v>
+        <v>0.1210243303015</v>
       </c>
       <c r="G48">
-        <v>-5.407883226525074</v>
+        <v>-8.834277996397518</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-7.326848931626961</v>
       </c>
       <c r="E49">
-        <v>-13.26715841798559</v>
+        <v>-13.97803373923568</v>
       </c>
       <c r="F49">
-        <v>1.667128184154429</v>
+        <v>0.2139704663652157</v>
       </c>
       <c r="G49">
-        <v>-6.890368692829487</v>
+        <v>-8.972986543947441</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.290669399401367</v>
       </c>
       <c r="E50">
-        <v>-12.22662830287314</v>
+        <v>-13.5945897311102</v>
       </c>
       <c r="F50">
-        <v>1.589480337285614</v>
+        <v>0.2171803900510638</v>
       </c>
       <c r="G50">
-        <v>-6.194349667016495</v>
+        <v>-9.361995508085041</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.278785972417761</v>
       </c>
       <c r="E51">
-        <v>-11.81358166015952</v>
+        <v>-13.69089225935732</v>
       </c>
       <c r="F51">
-        <v>1.285807474358538</v>
+        <v>-0.1776750147391681</v>
       </c>
       <c r="G51">
-        <v>-7.141265007614233</v>
+        <v>-9.090249377493965</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.28265635387721</v>
       </c>
       <c r="E52">
-        <v>-11.45425177612488</v>
+        <v>-12.38954015529908</v>
       </c>
       <c r="F52">
-        <v>1.466729542069172</v>
+        <v>-0.1760041976877215</v>
       </c>
       <c r="G52">
-        <v>-6.292368299343236</v>
+        <v>-9.723401143516199</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-7.293869493997861</v>
       </c>
       <c r="E53">
-        <v>-10.11493294598633</v>
+        <v>-12.32627737341192</v>
       </c>
       <c r="F53">
-        <v>1.230394665315668</v>
+        <v>-0.139999208525041</v>
       </c>
       <c r="G53">
-        <v>-6.937020900568896</v>
+        <v>-9.176108376054964</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.306637528015552</v>
       </c>
       <c r="E54">
-        <v>-10.61978081378345</v>
+        <v>-11.98323188190887</v>
       </c>
       <c r="F54">
-        <v>1.366429160203403</v>
+        <v>0.05536130301638881</v>
       </c>
       <c r="G54">
-        <v>-6.856620991602156</v>
+        <v>-9.290716152078993</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.316548389422459</v>
       </c>
       <c r="E55">
-        <v>-11.56294420925698</v>
+        <v>-11.91861055781941</v>
       </c>
       <c r="F55">
-        <v>1.347153050740258</v>
+        <v>-0.2702019968970673</v>
       </c>
       <c r="G55">
-        <v>-5.916141351532763</v>
+        <v>-9.569086684294151</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.324379949128245</v>
       </c>
       <c r="E56">
-        <v>-10.12968671430333</v>
+        <v>-11.26268826865241</v>
       </c>
       <c r="F56">
-        <v>1.327804044945667</v>
+        <v>-0.3584314089692426</v>
       </c>
       <c r="G56">
-        <v>-7.099744145460694</v>
+        <v>-9.197408426054634</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.330914563169628</v>
       </c>
       <c r="E57">
-        <v>-9.622416112912108</v>
+        <v>-11.23484721045325</v>
       </c>
       <c r="F57">
-        <v>1.594934308265646</v>
+        <v>-0.2313896706062993</v>
       </c>
       <c r="G57">
-        <v>-6.886985315288352</v>
+        <v>-9.456657247234961</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.342774856934231</v>
       </c>
       <c r="E58">
-        <v>-8.108162331857255</v>
+        <v>-11.61454617057439</v>
       </c>
       <c r="F58">
-        <v>1.654959467007304</v>
+        <v>-0.2825181634418903</v>
       </c>
       <c r="G58">
-        <v>-6.705348923730699</v>
+        <v>-9.924967019220263</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.363393007685135</v>
       </c>
       <c r="E59">
-        <v>-8.383507136945635</v>
+        <v>-10.76728226916129</v>
       </c>
       <c r="F59">
-        <v>1.860865095586372</v>
+        <v>-0.3912670644488123</v>
       </c>
       <c r="G59">
-        <v>-7.278050128205839</v>
+        <v>-9.784047027250107</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.401031903815021</v>
       </c>
       <c r="E60">
-        <v>-8.081471506056046</v>
+        <v>-10.78127072537098</v>
       </c>
       <c r="F60">
-        <v>0.8814101054554586</v>
+        <v>-0.2445532570041862</v>
       </c>
       <c r="G60">
-        <v>-6.852936354416948</v>
+        <v>-10.40693941264614</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.456329529370129</v>
       </c>
       <c r="E61">
-        <v>-8.528771526163684</v>
+        <v>-10.84865894707912</v>
       </c>
       <c r="F61">
-        <v>1.065900779937353</v>
+        <v>-0.3058955199162952</v>
       </c>
       <c r="G61">
-        <v>-8.157311160163031</v>
+        <v>-10.5529179182003</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.533005466943807</v>
       </c>
       <c r="E62">
-        <v>-7.734277932361967</v>
+        <v>-10.33100455478832</v>
       </c>
       <c r="F62">
-        <v>1.36915945916303</v>
+        <v>-0.125839924508989</v>
       </c>
       <c r="G62">
-        <v>-7.182537578852326</v>
+        <v>-10.54316505104161</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.62419871440293</v>
       </c>
       <c r="E63">
-        <v>-8.844600888880638</v>
+        <v>-10.67705242455846</v>
       </c>
       <c r="F63">
-        <v>1.127006129772262</v>
+        <v>-0.1362491892925676</v>
       </c>
       <c r="G63">
-        <v>-8.129542304179624</v>
+        <v>-10.16759028070237</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.726539082528149</v>
       </c>
       <c r="E64">
-        <v>-7.469312389699167</v>
+        <v>-10.25042488829583</v>
       </c>
       <c r="F64">
-        <v>1.691685964177823</v>
+        <v>-0.07038404036117335</v>
       </c>
       <c r="G64">
-        <v>-7.759668293259011</v>
+        <v>-11.44225294023349</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.827140233039595</v>
       </c>
       <c r="E65">
-        <v>-6.251180052479886</v>
+        <v>-10.47136460665606</v>
       </c>
       <c r="F65">
-        <v>1.204147015790563</v>
+        <v>-0.2859360073458411</v>
       </c>
       <c r="G65">
-        <v>-8.88005290956902</v>
+        <v>-10.59595832075637</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.918766479424235</v>
       </c>
       <c r="E66">
-        <v>-8.073478749432507</v>
+        <v>-9.918809265188139</v>
       </c>
       <c r="F66">
-        <v>0.9203367464478129</v>
+        <v>-0.3830935632853895</v>
       </c>
       <c r="G66">
-        <v>-8.004383819521937</v>
+        <v>-10.17429413541939</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.98805241303503</v>
       </c>
       <c r="E67">
-        <v>-8.559796101590234</v>
+        <v>-10.52787996227179</v>
       </c>
       <c r="F67">
-        <v>1.621360885149756</v>
+        <v>-0.1914814142416275</v>
       </c>
       <c r="G67">
-        <v>-8.455167563422338</v>
+        <v>-10.62294257744697</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.028317980575213</v>
       </c>
       <c r="E68">
-        <v>-8.169274088590766</v>
+        <v>-10.46865205072547</v>
       </c>
       <c r="F68">
-        <v>1.183278784179238</v>
+        <v>-0.07029126321205981</v>
       </c>
       <c r="G68">
-        <v>-8.989565756008112</v>
+        <v>-10.93822238187946</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.030030710210184</v>
       </c>
       <c r="E69">
-        <v>-7.397780614274005</v>
+        <v>-10.8929836506662</v>
       </c>
       <c r="F69">
-        <v>1.277391261546095</v>
+        <v>-0.4806048321059333</v>
       </c>
       <c r="G69">
-        <v>-8.360611761729675</v>
+        <v>-10.22553806982177</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.989342532988042</v>
       </c>
       <c r="E70">
-        <v>-7.570315473966246</v>
+        <v>-9.961707499462801</v>
       </c>
       <c r="F70">
-        <v>0.8909346738528473</v>
+        <v>-0.518076031571569</v>
       </c>
       <c r="G70">
-        <v>-7.83635045958515</v>
+        <v>-10.37227137975889</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.903046729359607</v>
       </c>
       <c r="E71">
-        <v>-8.424390200286883</v>
+        <v>-8.214314291071055</v>
       </c>
       <c r="F71">
-        <v>1.098687561740158</v>
+        <v>-0.07432209899408219</v>
       </c>
       <c r="G71">
-        <v>-7.299164787655311</v>
+        <v>-10.46348353045689</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.771416304976924</v>
       </c>
       <c r="E72">
-        <v>-8.408368459247745</v>
+        <v>-10.35078492925382</v>
       </c>
       <c r="F72">
-        <v>1.42486219679688</v>
+        <v>-0.2370300242519611</v>
       </c>
       <c r="G72">
-        <v>-8.550474858952416</v>
+        <v>-11.07284240568838</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.598565023206241</v>
       </c>
       <c r="E73">
-        <v>-7.437789682131773</v>
+        <v>-10.91170436221391</v>
       </c>
       <c r="F73">
-        <v>0.9909070222271085</v>
+        <v>-0.4252640910271068</v>
       </c>
       <c r="G73">
-        <v>-7.382262791236557</v>
+        <v>-10.90512023703228</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.387301892259027</v>
       </c>
       <c r="E74">
-        <v>-9.893626421231485</v>
+        <v>-10.70733885872176</v>
       </c>
       <c r="F74">
-        <v>1.191574055350872</v>
+        <v>-0.7759691699829306</v>
       </c>
       <c r="G74">
-        <v>-7.965014811968925</v>
+        <v>-10.21455036917693</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.146678891628881</v>
       </c>
       <c r="E75">
-        <v>-9.042160095939266</v>
+        <v>-10.87608791414358</v>
       </c>
       <c r="F75">
-        <v>0.8637493124277732</v>
+        <v>-0.7495939518777944</v>
       </c>
       <c r="G75">
-        <v>-8.214242611801877</v>
+        <v>-9.959350345191135</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.881084000506101</v>
       </c>
       <c r="E76">
-        <v>-8.372729368807379</v>
+        <v>-11.6147318380087</v>
       </c>
       <c r="F76">
-        <v>0.9356532597255758</v>
+        <v>-0.5831674853487485</v>
       </c>
       <c r="G76">
-        <v>-8.82336974884562</v>
+        <v>-10.39950723791047</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.602622327317123</v>
       </c>
       <c r="E77">
-        <v>-7.404414828695242</v>
+        <v>-10.86872461540711</v>
       </c>
       <c r="F77">
-        <v>0.6973236742661301</v>
+        <v>-0.6269541578933275</v>
       </c>
       <c r="G77">
-        <v>-7.643577392833389</v>
+        <v>-10.34535995507015</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.31666659091379</v>
       </c>
       <c r="E78">
-        <v>-9.105527032728597</v>
+        <v>-11.50965312713472</v>
       </c>
       <c r="F78">
-        <v>1.337999590939324</v>
+        <v>-0.6937023464761062</v>
       </c>
       <c r="G78">
-        <v>-7.745760691448534</v>
+        <v>-9.583325340658556</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.036320629770635</v>
       </c>
       <c r="E79">
-        <v>-9.848491120797034</v>
+        <v>-12.12260472644294</v>
       </c>
       <c r="F79">
-        <v>0.3798965989829707</v>
+        <v>-0.6789665187477057</v>
       </c>
       <c r="G79">
-        <v>-7.639925861103573</v>
+        <v>-9.580746425683463</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.766053858670427</v>
       </c>
       <c r="E80">
-        <v>-10.65695052843841</v>
+        <v>-12.55924471873653</v>
       </c>
       <c r="F80">
-        <v>0.6161287581785281</v>
+        <v>-0.9284807208797504</v>
       </c>
       <c r="G80">
-        <v>-8.826335997648806</v>
+        <v>-10.18607305644812</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.515382296574369</v>
       </c>
       <c r="E81">
-        <v>-11.20630423878291</v>
+        <v>-13.44264131425683</v>
       </c>
       <c r="F81">
-        <v>0.392220220834419</v>
+        <v>-0.575621058309245</v>
       </c>
       <c r="G81">
-        <v>-8.318604249381863</v>
+        <v>-9.887677034265913</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.283798210635632</v>
       </c>
       <c r="E82">
-        <v>-13.27848865995279</v>
+        <v>-13.65550223498737</v>
       </c>
       <c r="F82">
-        <v>0.497481695075555</v>
+        <v>-1.18401798239755</v>
       </c>
       <c r="G82">
-        <v>-6.727334256656999</v>
+        <v>-10.20745918063181</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.075369620308379</v>
       </c>
       <c r="E83">
-        <v>-13.53989482204556</v>
+        <v>-14.58686442719692</v>
       </c>
       <c r="F83">
-        <v>-0.03733880792869547</v>
+        <v>-0.9411464584685548</v>
       </c>
       <c r="G83">
-        <v>-5.857044803111232</v>
+        <v>-9.635059235800746</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.886748205155549</v>
       </c>
       <c r="E84">
-        <v>-13.13458281293704</v>
+        <v>-16.03195029625861</v>
       </c>
       <c r="F84">
-        <v>0.3704648077346955</v>
+        <v>-0.8018465392789844</v>
       </c>
       <c r="G84">
-        <v>-6.431997178553077</v>
+        <v>-9.727456561801805</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.71982071350551</v>
       </c>
       <c r="E85">
-        <v>-14.80534518417099</v>
+        <v>-16.63501170833408</v>
       </c>
       <c r="F85">
-        <v>-0.1929650202600414</v>
+        <v>-1.654369963911526</v>
       </c>
       <c r="G85">
-        <v>-6.834652211403553</v>
+        <v>-9.280976527102457</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.57221735979722</v>
       </c>
       <c r="E86">
-        <v>-15.37829224409545</v>
+        <v>-17.47877962781326</v>
       </c>
       <c r="F86">
-        <v>0.1372222264958415</v>
+        <v>-0.9519475410336576</v>
       </c>
       <c r="G86">
-        <v>-6.959300872048192</v>
+        <v>-9.361048692060809</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.447264328817002</v>
       </c>
       <c r="E87">
-        <v>-15.61836023666407</v>
+        <v>-18.52939012606679</v>
       </c>
       <c r="F87">
-        <v>-0.1834934673764319</v>
+        <v>-1.244359577487077</v>
       </c>
       <c r="G87">
-        <v>-6.700882997798222</v>
+        <v>-9.696850568291243</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.346388801128929</v>
       </c>
       <c r="E88">
-        <v>-18.1818342744521</v>
+        <v>-20.01703912232658</v>
       </c>
       <c r="F88">
-        <v>-0.2000980919655479</v>
+        <v>-1.123751768741678</v>
       </c>
       <c r="G88">
-        <v>-6.486247088305114</v>
+        <v>-9.770473790539095</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.277438957008902</v>
       </c>
       <c r="E89">
-        <v>-18.78706029710324</v>
+        <v>-20.67283461422138</v>
       </c>
       <c r="F89">
-        <v>-0.3445678521159901</v>
+        <v>-1.346612421321246</v>
       </c>
       <c r="G89">
-        <v>-7.130707677889497</v>
+        <v>-9.384358243202819</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.246575557644629</v>
       </c>
       <c r="E90">
-        <v>-20.45459839484372</v>
+        <v>-22.34437588298464</v>
       </c>
       <c r="F90">
-        <v>-0.3050986304748021</v>
+        <v>-1.462610365470066</v>
       </c>
       <c r="G90">
-        <v>-6.609581462370662</v>
+        <v>-9.43758188383768</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.265961322295293</v>
       </c>
       <c r="E91">
-        <v>-23.17799096373862</v>
+        <v>-24.48966346006034</v>
       </c>
       <c r="F91">
-        <v>-0.2430348595548547</v>
+        <v>-1.248768148804776</v>
       </c>
       <c r="G91">
-        <v>-6.609462282731248</v>
+        <v>-9.895460126828739</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.343209128169033</v>
       </c>
       <c r="E92">
-        <v>-26.23469733349409</v>
+        <v>-26.61519330504058</v>
       </c>
       <c r="F92">
-        <v>-0.4416748776439677</v>
+        <v>-1.888404464387457</v>
       </c>
       <c r="G92">
-        <v>-6.035069389485541</v>
+        <v>-9.421419800514959</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.490695381369278</v>
       </c>
       <c r="E93">
-        <v>-26.62357551042878</v>
+        <v>-28.01856287154362</v>
       </c>
       <c r="F93">
-        <v>-0.5773473759766792</v>
+        <v>-1.962053781802958</v>
       </c>
       <c r="G93">
-        <v>-6.425207249652032</v>
+        <v>-8.830391415934413</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.712430372268893</v>
       </c>
       <c r="E94">
-        <v>-28.69450554429853</v>
+        <v>-30.34353124029566</v>
       </c>
       <c r="F94">
-        <v>-0.7480440764671565</v>
+        <v>-1.414519495900541</v>
       </c>
       <c r="G94">
-        <v>-6.379720353942446</v>
+        <v>-9.301035122524901</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.012718656806127</v>
       </c>
       <c r="E95">
-        <v>-30.92717908430025</v>
+        <v>-32.98608601967964</v>
       </c>
       <c r="F95">
-        <v>-0.4362565264622562</v>
+        <v>-1.701827960785313</v>
       </c>
       <c r="G95">
-        <v>-8.135521149423548</v>
+        <v>-9.65389292937366</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.3917566240796</v>
       </c>
       <c r="E96">
-        <v>-34.35812760299761</v>
+        <v>-33.89510019266133</v>
       </c>
       <c r="F96">
-        <v>-0.3928161114920473</v>
+        <v>-1.506834416003323</v>
       </c>
       <c r="G96">
-        <v>-6.912499689759515</v>
+        <v>-9.714432875650312</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.835853378273261</v>
       </c>
       <c r="E97">
-        <v>-37.50817035052517</v>
+        <v>-36.97259678658601</v>
       </c>
       <c r="F97">
-        <v>-0.8940098681470546</v>
+        <v>-2.051297943943563</v>
       </c>
       <c r="G97">
-        <v>-6.69916813520888</v>
+        <v>-10.2248660290773</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.345174305078287</v>
       </c>
       <c r="E98">
-        <v>-38.55850461186424</v>
+        <v>-38.55802232938242</v>
       </c>
       <c r="F98">
-        <v>-0.7401265408311988</v>
+        <v>-1.930533573759034</v>
       </c>
       <c r="G98">
-        <v>-6.105037769458037</v>
+        <v>-10.28470413969963</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.883389774973362</v>
       </c>
       <c r="E99">
-        <v>-43.3535427135221</v>
+        <v>-41.93091354706444</v>
       </c>
       <c r="F99">
-        <v>-1.251160473864061</v>
+        <v>-1.907493362817569</v>
       </c>
       <c r="G99">
-        <v>-7.167418317374475</v>
+        <v>-10.02639882399799</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.465933747626958</v>
       </c>
       <c r="E100">
-        <v>-43.38161245965864</v>
+        <v>-44.05442369263726</v>
       </c>
       <c r="F100">
-        <v>-1.377322486045232</v>
+        <v>-2.05913844141106</v>
       </c>
       <c r="G100">
-        <v>-6.551822374346997</v>
+        <v>-9.714714272021151</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.01998880907248</v>
       </c>
       <c r="E101">
-        <v>-46.81448105133526</v>
+        <v>-45.70803673280415</v>
       </c>
       <c r="F101">
-        <v>-1.405738801430866</v>
+        <v>-2.242210122531959</v>
       </c>
       <c r="G101">
-        <v>-8.308930835316112</v>
+        <v>-9.784768726177669</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.61537313539894</v>
       </c>
       <c r="E102">
-        <v>-48.7500289583902</v>
+        <v>-48.61161615034575</v>
       </c>
       <c r="F102">
-        <v>-1.12277015336936</v>
+        <v>-2.275223877003131</v>
       </c>
       <c r="G102">
-        <v>-7.159797441543073</v>
+        <v>-10.02868972151117</v>
       </c>
     </row>
   </sheetData>
